--- a/Luban/MiniTemplate/Datas/room.xlsx
+++ b/Luban/MiniTemplate/Datas/room.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8437CF3E-370F-4DE5-9192-196975031305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B253D7BB-14B0-4C6F-8FB8-CD82B572FE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$A$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$A$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
     <author>jlart</author>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -97,27 +97,47 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Room1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>width</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Length</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间宽度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间长度</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>#备注</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间宽度（必须为奇数）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room1_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room1_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room1_3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>levelbelong</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间所属大关</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间高度（必须为奇数）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>height</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -547,15 +567,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="10" style="3"/>
-    <col min="5" max="5" width="18.125" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="10" style="3"/>
+    <col min="1" max="5" width="10" style="3"/>
+    <col min="6" max="6" width="18.125" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -563,19 +583,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>13</v>
-      </c>
       <c r="F1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -583,19 +609,23 @@
         <v>4</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>17</v>
-      </c>
       <c r="F2" s="10" t="s">
-        <v>17</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -604,8 +634,10 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -613,35 +645,84 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>16</v>
-      </c>
+      <c r="G4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="9"/>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8"/>
+    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="8">
         <v>1001</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="8">
+      <c r="C5" s="8">
         <v>1</v>
       </c>
+      <c r="D5" s="11" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8">
         <v>17</v>
       </c>
-      <c r="F5" s="8">
+      <c r="G5" s="8">
         <v>13</v>
       </c>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="8">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>11</v>
+      </c>
+      <c r="G6" s="8">
+        <v>11</v>
+      </c>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="8">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>9</v>
+      </c>
+      <c r="G7" s="8">
+        <v>7</v>
+      </c>
+      <c r="H7" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Luban/MiniTemplate/Datas/room.xlsx
+++ b/Luban/MiniTemplate/Datas/room.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B253D7BB-14B0-4C6F-8FB8-CD82B572FE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3434BD24-2015-4501-919A-DD0EDB3F2504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="1650" windowWidth="22980" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,13 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>1=普通房间</t>
+          <t>0=出生房间
+1=敌人房间
+2=Boss房间
+3=传送门房间
+4=宝箱房间
+5=商店房间
+6=走廊</t>
         </r>
       </text>
     </comment>

--- a/Luban/MiniTemplate/Datas/room.xlsx
+++ b/Luban/MiniTemplate/Datas/room.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3434BD24-2015-4501-919A-DD0EDB3F2504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8EFEED-7FC8-4684-BAE8-3581F2564433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="1650" windowWidth="22980" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4830" yWindow="3075" windowWidth="22980" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,15 +45,134 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0=出生房间
-1=敌人房间
-2=Boss房间
-3=传送门房间
-4=宝箱房间
-5=商店房间
-6=走廊</t>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0=基础房间</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1=出生房间
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">=敌人房间
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>3</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">=Boss房间
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>4</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">=传送门房间
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>5</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">=宝箱房间
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>6</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">=商店房间
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>7</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>=走廊</t>
         </r>
       </text>
     </comment>
@@ -62,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -88,9 +207,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>类型</t>
-  </si>
-  <si>
     <t>path</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -103,7 +219,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>width</t>
+    <t>#备注</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属关卡ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>levelid</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -111,39 +235,79 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>#备注</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间宽度（必须为奇数）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room1_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room1_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room1_3</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>levelbelong</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间所属大关</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间高度（必须为奇数）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>height</t>
+    <t>房间可用作的类型</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room15×15</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-Room21×21-2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-Room15×15</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-Room21×21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-Room21×21-1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-Room25×15</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room15×21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room21×15</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room21×21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room21×25</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room25×15</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hor5×24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ver5×24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|2|1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TeleportRoom</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room11×11</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room21×13</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room19×13</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -162,12 +326,14 @@
     <font>
       <sz val="8"/>
       <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -175,17 +341,20 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -573,15 +742,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="10" style="3"/>
-    <col min="6" max="6" width="18.125" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="10" style="3"/>
+    <col min="1" max="3" width="10" style="3"/>
+    <col min="4" max="4" width="11.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.375" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="10" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -589,25 +759,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -615,23 +779,17 @@
         <v>4</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="10"/>
-    </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -640,10 +798,8 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -651,84 +807,270 @@
         <v>7</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="8">
         <v>1001</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="8">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>17</v>
-      </c>
-      <c r="G5" s="8">
-        <v>13</v>
-      </c>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="8">
         <v>1002</v>
       </c>
       <c r="C6" s="8">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>11</v>
-      </c>
-      <c r="G6" s="8">
-        <v>11</v>
-      </c>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="8">
         <v>1003</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
-        <v>9</v>
-      </c>
-      <c r="G7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="8">
+        <v>101</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2</v>
+      </c>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="8">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="8">
+        <v>101</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="8">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="8">
+        <v>101</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2</v>
+      </c>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="8">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="8">
+        <v>101</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2</v>
+      </c>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="8">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="8">
+        <v>101</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="8">
+        <v>101</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="8">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="8">
+        <v>101</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="8">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="8">
+        <v>101</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="8">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="8">
+        <v>101</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="8">
         <v>7</v>
       </c>
-      <c r="H7" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="8">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="8">
+        <v>101</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="8">
+        <v>7</v>
+      </c>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="8">
+        <v>101</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4</v>
+      </c>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="8">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="8">
+        <v>101</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="8">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="8">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="8">
+        <v>101</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5</v>
+      </c>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="8">
+        <v>1017</v>
+      </c>
+      <c r="C21" s="8">
+        <v>101</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="8">
+        <v>6</v>
+      </c>
+      <c r="F21" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Luban/MiniTemplate/Datas/room.xlsx
+++ b/Luban/MiniTemplate/Datas/room.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8EFEED-7FC8-4684-BAE8-3581F2564433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CB669D-3659-4452-861C-25786EA035FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4830" yWindow="3075" windowWidth="22980" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -239,58 +239,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Room15×15</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>E-Room21×21-2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>E-Room15×15</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>E-Room21×21</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>E-Room21×21-1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>E-Room25×15</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room15×21</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room21×15</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room21×21</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room21×25</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room25×15</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hor5×24</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ver5×24</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>0|2|1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -299,16 +247,53 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Room11×11</t>
+    <t>Room15x15</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Room21×13</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Room19×13</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>E-Room21x21-2</t>
+  </si>
+  <si>
+    <t>E-Room15x15</t>
+  </si>
+  <si>
+    <t>E-Room21x21</t>
+  </si>
+  <si>
+    <t>E-Room21x21-1</t>
+  </si>
+  <si>
+    <t>E-Room25x15</t>
+  </si>
+  <si>
+    <t>Room15x21</t>
+  </si>
+  <si>
+    <t>Room21x15</t>
+  </si>
+  <si>
+    <t>Room21x21</t>
+  </si>
+  <si>
+    <t>Room21x25</t>
+  </si>
+  <si>
+    <t>Room25x15</t>
+  </si>
+  <si>
+    <t>Hor5x24</t>
+  </si>
+  <si>
+    <t>Ver5x24</t>
+  </si>
+  <si>
+    <t>Room11x11</t>
+  </si>
+  <si>
+    <t>Room21x13</t>
+  </si>
+  <si>
+    <t>Room19x13</t>
   </si>
 </sst>
 </file>
@@ -824,11 +809,11 @@
       <c r="C5" s="8">
         <v>101</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>29</v>
       </c>
       <c r="F5" s="8"/>
     </row>
@@ -840,7 +825,7 @@
         <v>101</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" s="8">
         <v>3</v>
@@ -855,7 +840,7 @@
         <v>101</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" s="8">
         <v>2</v>
@@ -870,7 +855,7 @@
         <v>101</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" s="8">
         <v>2</v>
@@ -885,7 +870,7 @@
         <v>101</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E9" s="8">
         <v>2</v>
@@ -900,7 +885,7 @@
         <v>101</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E10" s="8">
         <v>2</v>
@@ -915,7 +900,7 @@
         <v>101</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" s="8">
         <v>2</v>
@@ -930,7 +915,7 @@
         <v>101</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12" s="8">
         <v>2</v>
@@ -945,7 +930,7 @@
         <v>101</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="8">
         <v>2</v>
@@ -960,7 +945,7 @@
         <v>101</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E14" s="8">
         <v>2</v>
@@ -975,7 +960,7 @@
         <v>101</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="8">
         <v>2</v>
@@ -990,7 +975,7 @@
         <v>101</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="8">
         <v>7</v>
@@ -1005,7 +990,7 @@
         <v>101</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E17" s="8">
         <v>7</v>
@@ -1020,7 +1005,7 @@
         <v>101</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E18" s="8">
         <v>4</v>
